--- a/summary_report_JP.xlsx
+++ b/summary_report_JP.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>文件名称</t>
   </si>
@@ -38,9 +38,15 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
+    <t>All order-2026-01-19-04_50.csv</t>
+  </si>
+  <si>
     <t>All order-2026-01-12-03_05.csv</t>
   </si>
   <si>
+    <t>2026-01-18</t>
+  </si>
+  <si>
     <t>2026-01-11</t>
   </si>
   <si>
@@ -48,6 +54,12 @@
   </si>
   <si>
     <t>电动剃眉刀</t>
+  </si>
+  <si>
+    <t>白色睫毛推</t>
+  </si>
+  <si>
+    <t>车载手机支架</t>
   </si>
 </sst>
 </file>
@@ -405,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -436,21 +448,44 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>70810</v>
+      </c>
+      <c r="D2">
+        <v>69844</v>
+      </c>
+      <c r="E2">
+        <v>298.4</v>
+      </c>
+      <c r="F2">
+        <v>922.4</v>
+      </c>
+      <c r="G2">
+        <v>247.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
         <v>33534</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>32337</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>151.8</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>412.5</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>119.7</v>
       </c>
     </row>
@@ -461,23 +496,51 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2">
+        <v>38</v>
+      </c>
+      <c r="C2">
         <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
